--- a/release_1_0_0/data/files/output/sim_v1/eval_sim_v1_loo.xlsx
+++ b/release_1_0_0/data/files/output/sim_v1/eval_sim_v1_loo.xlsx
@@ -560,25 +560,25 @@
         <v>14139.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9594</v>
+        <v>0.9518884587112851</v>
       </c>
       <c r="M2" t="n">
-        <v>4125.77</v>
+        <v>3432.306971428518</v>
       </c>
       <c r="N2" t="n">
-        <v>3958.4</v>
+        <v>3267.173392857091</v>
       </c>
       <c r="O2" t="n">
-        <v>167.37</v>
+        <v>165.1335785714284</v>
       </c>
       <c r="P2" t="n">
-        <v>21.29</v>
+        <v>1977.989434346401</v>
       </c>
       <c r="Q2" t="n">
-        <v>564.4299999999999</v>
+        <v>623.8571428571429</v>
       </c>
       <c r="R2" t="n">
-        <v>307.8</v>
+        <v>330.5</v>
       </c>
       <c r="S2" t="n">
         <v>28</v>
@@ -629,28 +629,28 @@
         <v>33554.88</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.782491252601076</v>
       </c>
       <c r="M3" t="n">
-        <v>17839.96</v>
+        <v>17096.63041667935</v>
       </c>
       <c r="N3" t="n">
-        <v>13225.77</v>
+        <v>13377.96375000341</v>
       </c>
       <c r="O3" t="n">
-        <v>4614.2</v>
+        <v>3718.666666666654</v>
       </c>
       <c r="P3" t="n">
-        <v>1396.28</v>
+        <v>8864.534661573482</v>
       </c>
       <c r="Q3" t="n">
-        <v>3772.78</v>
+        <v>3615.583333333333</v>
       </c>
       <c r="R3" t="n">
-        <v>1354.7</v>
+        <v>1298.25</v>
       </c>
       <c r="S3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -701,22 +701,22 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1125.05</v>
+        <v>1438.426056822751</v>
       </c>
       <c r="N4" t="n">
-        <v>1125.05</v>
+        <v>1438.426056822751</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>101.33</v>
+        <v>795.1738730737154</v>
       </c>
       <c r="Q4" t="n">
-        <v>353.4</v>
+        <v>423.5238095238095</v>
       </c>
       <c r="R4" t="n">
-        <v>322.83</v>
+        <v>327.2857142857143</v>
       </c>
       <c r="S4" t="n">
         <v>21</v>
@@ -767,25 +767,25 @@
         <v>18841.68</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5663</v>
+        <v>0.2914964190077363</v>
       </c>
       <c r="M5" t="n">
-        <v>1585.06</v>
+        <v>1766.508730769235</v>
       </c>
       <c r="N5" t="n">
-        <v>897.67</v>
+        <v>517.1171923076913</v>
       </c>
       <c r="O5" t="n">
-        <v>687.39</v>
+        <v>1256.891538461542</v>
       </c>
       <c r="P5" t="n">
-        <v>123.75</v>
+        <v>815.1594794547862</v>
       </c>
       <c r="Q5" t="n">
-        <v>223.33</v>
+        <v>208.2307692307692</v>
       </c>
       <c r="R5" t="n">
-        <v>128.4</v>
+        <v>113.6923076923077</v>
       </c>
       <c r="S5" t="n">
         <v>26</v>
@@ -827,37 +827,37 @@
         <v>1.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>4815.83</v>
+        <v>4815.828</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6191</v>
+        <v>0.5906450896391696</v>
       </c>
       <c r="M6" t="n">
-        <v>439.71</v>
+        <v>570.2660606060817</v>
       </c>
       <c r="N6" t="n">
-        <v>272.22</v>
+        <v>336.8248484848553</v>
       </c>
       <c r="O6" t="n">
-        <v>167.49</v>
+        <v>233.4412121212121</v>
       </c>
       <c r="P6" t="n">
-        <v>-165.85</v>
+        <v>248.7434418642236</v>
       </c>
       <c r="Q6" t="n">
-        <v>138.05</v>
+        <v>164.0909090909091</v>
       </c>
       <c r="R6" t="n">
-        <v>101.05</v>
+        <v>118.2121212121212</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -902,28 +902,28 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3520.61</v>
+        <v>3520.614999999999</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1088.19</v>
+        <v>1085.428421052641</v>
       </c>
       <c r="N7" t="n">
-        <v>1088.19</v>
+        <v>1085.428421052641</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-41.52</v>
+        <v>607.1911078395337</v>
       </c>
       <c r="Q7" t="n">
-        <v>347.97</v>
+        <v>408.4736842105263</v>
       </c>
       <c r="R7" t="n">
-        <v>164.07</v>
+        <v>188.3157894736842</v>
       </c>
       <c r="S7" t="n">
         <v>19</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4125.77</v>
+        <v>3432.306971428518</v>
       </c>
       <c r="D2" t="n">
-        <v>13763.77397182734</v>
+        <v>12943.6172929705</v>
       </c>
       <c r="E2" t="n">
-        <v>9638.00397182734</v>
+        <v>9511.310321541978</v>
       </c>
       <c r="F2" t="n">
-        <v>21.29</v>
+        <v>1977.989434346401</v>
       </c>
       <c r="G2" t="n">
-        <v>8089.263722709286</v>
+        <v>7585.123088092538</v>
       </c>
       <c r="H2" t="n">
-        <v>8067.973722709286</v>
+        <v>5607.133653746137</v>
       </c>
       <c r="I2" t="n">
         <v>28</v>
@@ -1035,25 +1035,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17839.96</v>
+        <v>17096.63041667935</v>
       </c>
       <c r="D3" t="n">
-        <v>13202.17095293028</v>
+        <v>11214.12394927665</v>
       </c>
       <c r="E3" t="n">
-        <v>4637.789047069718</v>
+        <v>5882.5064674027</v>
       </c>
       <c r="F3" t="n">
-        <v>1396.28</v>
+        <v>8864.534661573482</v>
       </c>
       <c r="G3" t="n">
-        <v>7948.472074879434</v>
+        <v>6730.665632752527</v>
       </c>
       <c r="H3" t="n">
-        <v>6552.192074879435</v>
+        <v>2133.869028820955</v>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1125.05</v>
+        <v>1438.426056822751</v>
       </c>
       <c r="D4" t="n">
-        <v>795.8292544112999</v>
+        <v>14.43194200702249</v>
       </c>
       <c r="E4" t="n">
-        <v>329.2207455887001</v>
+        <v>1423.994114815729</v>
       </c>
       <c r="F4" t="n">
-        <v>101.33</v>
+        <v>795.1738730737154</v>
       </c>
       <c r="G4" t="n">
-        <v>537.2238814061591</v>
+        <v>235.8325201049423</v>
       </c>
       <c r="H4" t="n">
-        <v>435.8938814061591</v>
+        <v>559.3413529687732</v>
       </c>
       <c r="I4" t="n">
         <v>21</v>
@@ -1101,22 +1101,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1585.06</v>
+        <v>1766.508730769235</v>
       </c>
       <c r="D5" t="n">
-        <v>4156.761461920194</v>
+        <v>5019.058701268536</v>
       </c>
       <c r="E5" t="n">
-        <v>2571.701461920194</v>
+        <v>3252.549970499301</v>
       </c>
       <c r="F5" t="n">
-        <v>123.75</v>
+        <v>815.1594794547862</v>
       </c>
       <c r="G5" t="n">
-        <v>2309.326311137449</v>
+        <v>2682.400190787595</v>
       </c>
       <c r="H5" t="n">
-        <v>2185.576311137449</v>
+        <v>1867.240711332808</v>
       </c>
       <c r="I5" t="n">
         <v>26</v>
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>439.71</v>
+        <v>570.2660606060817</v>
       </c>
       <c r="D6" t="n">
-        <v>2291.580028164406</v>
+        <v>3880.389206051172</v>
       </c>
       <c r="E6" t="n">
-        <v>1851.870028164406</v>
+        <v>3310.12314544509</v>
       </c>
       <c r="F6" t="n">
-        <v>-165.85</v>
+        <v>248.7434418642236</v>
       </c>
       <c r="G6" t="n">
-        <v>1362.035394617088</v>
+        <v>2336.165779813132</v>
       </c>
       <c r="H6" t="n">
-        <v>1527.885394617088</v>
+        <v>2087.422337948909</v>
       </c>
       <c r="I6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -1167,22 +1167,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1088.19</v>
+        <v>1085.428421052641</v>
       </c>
       <c r="D7" t="n">
-        <v>379.4183245949843</v>
+        <v>288.1948866155714</v>
       </c>
       <c r="E7" t="n">
-        <v>708.7716754050157</v>
+        <v>797.2335344370694</v>
       </c>
       <c r="F7" t="n">
-        <v>-41.52</v>
+        <v>607.1911078395337</v>
       </c>
       <c r="G7" t="n">
-        <v>226.7255004103966</v>
+        <v>194.3561657711298</v>
       </c>
       <c r="H7" t="n">
-        <v>268.2455004103966</v>
+        <v>412.834942068404</v>
       </c>
       <c r="I7" t="n">
         <v>19</v>
@@ -1244,38 +1244,38 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>3289.559488329229</v>
+        <v>4029.619592356978</v>
       </c>
       <c r="D2" t="n">
-        <v>3172.961147526636</v>
+        <v>2111.307004480997</v>
       </c>
       <c r="E2" t="n">
-        <v>156.2334840672533</v>
+        <v>208.0899347379712</v>
       </c>
       <c r="F2" t="n">
-        <v>7021.411069991372</v>
+        <v>252.3554515929449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SIMPLY</t>
+          <t>LIBERTY</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1280.320851784711</v>
+        <v>2338.272042657515</v>
       </c>
       <c r="D3" t="n">
-        <v>898.0654475137424</v>
+        <v>1213.291032150791</v>
       </c>
       <c r="E3" t="n">
-        <v>243.1451069049069</v>
+        <v>141.5598737218675</v>
       </c>
       <c r="F3" t="n">
-        <v>783.6543414433454</v>
+        <v>149.7032424178829</v>
       </c>
     </row>
     <row r="4">
@@ -1288,38 +1288,38 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>7137.896509448529</v>
+        <v>7696.908394472339</v>
       </c>
       <c r="D4" t="n">
-        <v>7310.082898794361</v>
+        <v>3870.501341283546</v>
       </c>
       <c r="E4" t="n">
-        <v>129.8008042687997</v>
+        <v>155.7593491849925</v>
       </c>
       <c r="F4" t="n">
-        <v>19182.43143971156</v>
+        <v>153.7742005383695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LIBERTY</t>
+          <t>SIMPLY</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1450.461103754447</v>
+        <v>2053.67833994108</v>
       </c>
       <c r="D5" t="n">
-        <v>1310.735096271804</v>
+        <v>1250.128640008656</v>
       </c>
       <c r="E5" t="n">
-        <v>95.75454102805327</v>
+        <v>326.9505813070535</v>
       </c>
       <c r="F5" t="n">
-        <v>1098.147428819209</v>
+        <v>453.5889118225821</v>
       </c>
     </row>
   </sheetData>

--- a/release_1_0_0/data/files/output/sim_v1/eval_sim_v1_loo.xlsx
+++ b/release_1_0_0/data/files/output/sim_v1/eval_sim_v1_loo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,70 +656,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H6188</t>
+          <t>HB6A3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LIBERTY</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MER BOUL</t>
+          <t>IBB STRA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mercure Paris Boulogne</t>
+          <t>Ibis budget Strasbourg Centre République</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MERCURE</t>
+          <t>IBIS BUDGET</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>191</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>8505.23</v>
+        <v>3520.614999999999</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1438.426056822751</v>
+        <v>1085.428421052641</v>
       </c>
       <c r="N4" t="n">
-        <v>1438.426056822751</v>
+        <v>1085.428421052641</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>795.1738730737154</v>
+        <v>607.1911078395337</v>
       </c>
       <c r="Q4" t="n">
-        <v>423.5238095238095</v>
+        <v>408.4736842105263</v>
       </c>
       <c r="R4" t="n">
-        <v>327.2857142857143</v>
+        <v>188.3157894736842</v>
       </c>
       <c r="S4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -858,75 +858,6 @@
       </c>
       <c r="S6" t="n">
         <v>33</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HB6A3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SIMPLY</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>IBB STRA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ibis budget Strasbourg Centre République</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>IBIS BUDGET</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>97</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3520.614999999999</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1085.428421052641</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1085.428421052641</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>607.1911078395337</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>408.4736842105263</v>
-      </c>
-      <c r="R7" t="n">
-        <v>188.3157894736842</v>
-      </c>
-      <c r="S7" t="n">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -940,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,19 +936,19 @@
         <v>3432.306971428518</v>
       </c>
       <c r="D2" t="n">
-        <v>12943.6172929705</v>
+        <v>9399.281631452177</v>
       </c>
       <c r="E2" t="n">
-        <v>9511.310321541978</v>
+        <v>5966.974660023659</v>
       </c>
       <c r="F2" t="n">
         <v>1977.989434346401</v>
       </c>
       <c r="G2" t="n">
-        <v>7585.123088092538</v>
+        <v>5697.454638885537</v>
       </c>
       <c r="H2" t="n">
-        <v>5607.133653746137</v>
+        <v>3719.465204539136</v>
       </c>
       <c r="I2" t="n">
         <v>28</v>
@@ -1038,19 +969,19 @@
         <v>17096.63041667935</v>
       </c>
       <c r="D3" t="n">
-        <v>11214.12394927665</v>
+        <v>12901.49391833254</v>
       </c>
       <c r="E3" t="n">
-        <v>5882.5064674027</v>
+        <v>4195.136498346814</v>
       </c>
       <c r="F3" t="n">
         <v>8864.534661573482</v>
       </c>
       <c r="G3" t="n">
-        <v>6730.665632752527</v>
+        <v>7717.090207526566</v>
       </c>
       <c r="H3" t="n">
-        <v>2133.869028820955</v>
+        <v>1147.444454046916</v>
       </c>
       <c r="I3" t="n">
         <v>24</v>
@@ -1059,34 +990,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H6188</t>
+          <t>HB6A3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LIBERTY</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1438.426056822751</v>
+        <v>1085.428421052641</v>
       </c>
       <c r="D4" t="n">
-        <v>14.43194200702249</v>
+        <v>2595.850996817688</v>
       </c>
       <c r="E4" t="n">
-        <v>1423.994114815729</v>
+        <v>1510.422575765047</v>
       </c>
       <c r="F4" t="n">
-        <v>795.1738730737154</v>
+        <v>607.1911078395337</v>
       </c>
       <c r="G4" t="n">
-        <v>235.8325201049423</v>
+        <v>1787.018375218478</v>
       </c>
       <c r="H4" t="n">
-        <v>559.3413529687732</v>
+        <v>1179.827267378944</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -1104,19 +1035,19 @@
         <v>1766.508730769235</v>
       </c>
       <c r="D5" t="n">
-        <v>5019.058701268536</v>
+        <v>2436.999190769234</v>
       </c>
       <c r="E5" t="n">
-        <v>3252.549970499301</v>
+        <v>670.4904599999991</v>
       </c>
       <c r="F5" t="n">
         <v>815.1594794547862</v>
       </c>
       <c r="G5" t="n">
-        <v>2682.400190787595</v>
+        <v>1306.807300532546</v>
       </c>
       <c r="H5" t="n">
-        <v>1867.240711332808</v>
+        <v>491.6478210777598</v>
       </c>
       <c r="I5" t="n">
         <v>26</v>
@@ -1137,55 +1068,22 @@
         <v>570.2660606060817</v>
       </c>
       <c r="D6" t="n">
-        <v>3880.389206051172</v>
+        <v>808.977587878798</v>
       </c>
       <c r="E6" t="n">
-        <v>3310.12314544509</v>
+        <v>238.7115272727162</v>
       </c>
       <c r="F6" t="n">
         <v>248.7434418642236</v>
       </c>
       <c r="G6" t="n">
-        <v>2336.165779813132</v>
+        <v>403.1245808857871</v>
       </c>
       <c r="H6" t="n">
-        <v>2087.422337948909</v>
+        <v>154.3811390215635</v>
       </c>
       <c r="I6" t="n">
         <v>33</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HB6A3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SIMPLY</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1085.428421052641</v>
-      </c>
-      <c r="D7" t="n">
-        <v>288.1948866155714</v>
-      </c>
-      <c r="E7" t="n">
-        <v>797.2335344370694</v>
-      </c>
-      <c r="F7" t="n">
-        <v>607.1911078395337</v>
-      </c>
-      <c r="G7" t="n">
-        <v>194.3561657711298</v>
-      </c>
-      <c r="H7" t="n">
-        <v>412.834942068404</v>
-      </c>
-      <c r="I7" t="n">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1241,19 +1139,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>4029.619592356978</v>
+        <v>2516.347144281647</v>
       </c>
       <c r="D2" t="n">
-        <v>2111.307004480997</v>
+        <v>1338.553177212864</v>
       </c>
       <c r="E2" t="n">
-        <v>208.0899347379712</v>
+        <v>83.47100260259647</v>
       </c>
       <c r="F2" t="n">
-        <v>252.3554515929449</v>
+        <v>103.5346955221745</v>
       </c>
     </row>
     <row r="3">
@@ -1263,19 +1161,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2338.272042657515</v>
+        <v>670.4904599999991</v>
       </c>
       <c r="D3" t="n">
-        <v>1213.291032150791</v>
+        <v>491.6478210777598</v>
       </c>
       <c r="E3" t="n">
-        <v>141.5598737218675</v>
+        <v>37.95568333862867</v>
       </c>
       <c r="F3" t="n">
-        <v>149.7032424178829</v>
+        <v>60.31308393869076</v>
       </c>
     </row>
     <row r="4">
@@ -1285,19 +1183,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7696.908394472339</v>
+        <v>3890.844578045173</v>
       </c>
       <c r="D4" t="n">
-        <v>3870.501341283546</v>
+        <v>2015.578975321665</v>
       </c>
       <c r="E4" t="n">
-        <v>155.7593491849925</v>
+        <v>112.5132177765898</v>
       </c>
       <c r="F4" t="n">
-        <v>153.7742005383695</v>
+        <v>131.7653293092115</v>
       </c>
     </row>
     <row r="5">
@@ -1307,19 +1205,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>2053.67833994108</v>
+        <v>238.7115272727162</v>
       </c>
       <c r="D5" t="n">
-        <v>1250.128640008656</v>
+        <v>154.3811390215635</v>
       </c>
       <c r="E5" t="n">
-        <v>326.9505813070535</v>
+        <v>41.85967634458421</v>
       </c>
       <c r="F5" t="n">
-        <v>453.5889118225821</v>
+        <v>62.06440574454714</v>
       </c>
     </row>
   </sheetData>

--- a/release_1_0_0/data/files/output/sim_v1/eval_sim_v1_loo.xlsx
+++ b/release_1_0_0/data/files/output/sim_v1/eval_sim_v1_loo.xlsx
@@ -871,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,35 +887,45 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>eval_biased</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_solution_hotels</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>ca_reel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ca_pred</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ca_err_abs</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>marge_reel</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>marge_pred</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>marge_err_abs</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>n_mois</t>
         </is>
@@ -932,25 +942,31 @@
           <t>CONNECTED</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
         <v>3432.306971428518</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>9399.281631452177</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>5966.974660023659</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1977.989434346401</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>5697.454638885537</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>3719.465204539136</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>28</v>
       </c>
     </row>
@@ -965,25 +981,31 @@
           <t>CONNECTED</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
         <v>17096.63041667935</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>12901.49391833254</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>4195.136498346814</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>8864.534661573482</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>7717.090207526566</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>1147.444454046916</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>24</v>
       </c>
     </row>
@@ -998,25 +1020,31 @@
           <t>CONNECTED</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
         <v>1085.428421052641</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>2595.850996817688</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>1510.422575765047</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>607.1911078395337</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>1787.018375218478</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>1179.827267378944</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1031,25 +1059,31 @@
           <t>LIBERTY</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>1766.508730769235</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>2436.999190769234</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>670.4904599999991</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>815.1594794547862</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>1306.807300532546</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>491.6478210777598</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1064,25 +1098,31 @@
           <t>SIMPLY</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>570.2660606060817</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>808.977587878798</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>238.7115272727162</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>248.7434418642236</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>403.1245808857871</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>154.3811390215635</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>33</v>
       </c>
     </row>
@@ -1157,67 +1197,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LIBERTY</t>
+          <t>SIMPLY</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>670.4904599999991</v>
+        <v>238.7115272727162</v>
       </c>
       <c r="D3" t="n">
-        <v>491.6478210777598</v>
+        <v>154.3811390215635</v>
       </c>
       <c r="E3" t="n">
-        <v>37.95568333862867</v>
+        <v>41.85967634458421</v>
       </c>
       <c r="F3" t="n">
-        <v>60.31308393869076</v>
+        <v>62.06440574454714</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CONNECTED</t>
+          <t>LIBERTY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3890.844578045173</v>
+        <v>670.4904599999991</v>
       </c>
       <c r="D4" t="n">
-        <v>2015.578975321665</v>
+        <v>491.6478210777598</v>
       </c>
       <c r="E4" t="n">
-        <v>112.5132177765898</v>
+        <v>37.95568333862867</v>
       </c>
       <c r="F4" t="n">
-        <v>131.7653293092115</v>
+        <v>60.31308393869076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SIMPLY</t>
+          <t>CONNECTED</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>238.7115272727162</v>
+        <v>3890.844578045173</v>
       </c>
       <c r="D5" t="n">
-        <v>154.3811390215635</v>
+        <v>2015.578975321665</v>
       </c>
       <c r="E5" t="n">
-        <v>41.85967634458421</v>
+        <v>112.5132177765898</v>
       </c>
       <c r="F5" t="n">
-        <v>62.06440574454714</v>
+        <v>131.7653293092115</v>
       </c>
     </row>
   </sheetData>
